--- a/314e-ig/output/StructureDefinition-diagnosticreport-lab-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-lab-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -316,7 +316,7 @@
     <t>DiagnosticReport.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-lab-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-lab-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$69</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2539" uniqueCount="497">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1240,23 +1240,358 @@
     <t>DiagnosticReport.presentedForm</t>
   </si>
   <si>
+    <t xml:space="preserve">Attachment
+</t>
+  </si>
+  <si>
+    <t>Entire report as issued</t>
+  </si>
+  <si>
+    <t>Rich text representation of the entire result as issued by the diagnostic service. Multiple formats are allowed but they SHALL be semantically equivalent.</t>
+  </si>
+  <si>
+    <t>"application/pdf" is recommended as the most reliable and interoperable in this context.</t>
+  </si>
+  <si>
+    <t>Gives laboratory the ability to provide its own fully formatted report for clinical fidelity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:title}
+</t>
+  </si>
+  <si>
+    <t>text (type=ED)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report</t>
+  </si>
+  <si>
+    <t>report</t>
+  </si>
+  <si>
     <t xml:space="preserve">Attachment {http://314e.com/fhir/StructureDefinition/attachment-314e}
 </t>
   </si>
   <si>
-    <t>Entire report as issued</t>
-  </si>
-  <si>
-    <t>Rich text representation of the entire result as issued by the diagnostic service. Multiple formats are allowed but they SHALL be semantically equivalent.</t>
-  </si>
-  <si>
-    <t>"application/pdf" is recommended as the most reliable and interoperable in this context.</t>
-  </si>
-  <si>
-    <t>Gives laboratory the ability to provide its own fully formatted report for clinical fidelity.</t>
-  </si>
-  <si>
-    <t>text (type=ED)</t>
+    <t>DiagnosticReport.presentedForm:report.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.extension:tag</t>
+  </si>
+  <si>
+    <t>tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/attachment-tag}
+</t>
+  </si>
+  <si>
+    <t>Semantic categorization tag associated with the attachment</t>
+  </si>
+  <si>
+    <t>A categorization or semantic tag associated with an Attachment.
+This extension allows multiple tags to be associated with an
+Attachment for workflow, classification, indexing, retrieval,
+processing, or application behavior purposes.</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.extension:helperFile</t>
+  </si>
+  <si>
+    <t>helperFile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/attachment-helperFile}
+</t>
+  </si>
+  <si>
+    <t>Helper file associated with the attachment</t>
+  </si>
+  <si>
+    <t>Provides the path or filename of an auxiliary/helper file required
+for interpretation, transformation, rendering, or processing of
+the attachment content.</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.contentType</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.contentType</t>
+  </si>
+  <si>
+    <t>Mime type of the content, with charset etc.</t>
+  </si>
+  <si>
+    <t>Identifies the type of the data in the attachment and allows a method to be chosen to interpret or render the data. Includes mime type parameters such as charset where appropriate.</t>
+  </si>
+  <si>
+    <t>Processors of the data need to be able to know how to interpret the data.</t>
+  </si>
+  <si>
+    <t>text/plain; charset=UTF-8, image/png</t>
+  </si>
+  <si>
+    <t>The mime type of an attachment. Any valid mime type is allowed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/mimetypes|4.0.1</t>
+  </si>
+  <si>
+    <t>Attachment.contentType</t>
+  </si>
+  <si>
+    <t>ED.2+ED.3/RP.2+RP.3. Note conversion may be needed if old style values are being used</t>
+  </si>
+  <si>
+    <t>./mediaType, ./charset</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.language</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.language</t>
+  </si>
+  <si>
+    <t>Human language of the content (BCP-47)</t>
+  </si>
+  <si>
+    <t>The human language of the content. The value can be any valid value according to BCP 47.</t>
+  </si>
+  <si>
+    <t>Users need to be able to choose between the languages in a set of attachments.</t>
+  </si>
+  <si>
+    <t>en-AU</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Attachment.language</t>
+  </si>
+  <si>
+    <t>./language</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base64Binary
+</t>
+  </si>
+  <si>
+    <t>Inline attachment data is prohibited</t>
+  </si>
+  <si>
+    <t>Inline binary data SHALL NOT be populated.
+Attachment content SHALL instead be persisted externally
+and referenced using Attachment.url.</t>
+  </si>
+  <si>
+    <t>The base64-encoded data SHALL be expressed in the same character set as the base resource XML or JSON.</t>
+  </si>
+  <si>
+    <t>The data needs to able to be transmitted inline.</t>
+  </si>
+  <si>
+    <t>Attachment.data</t>
+  </si>
+  <si>
+    <t>ED.5</t>
+  </si>
+  <si>
+    <t>./data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url
+</t>
+  </si>
+  <si>
+    <t>Object storage path or external attachment location</t>
+  </si>
+  <si>
+    <t>Reference/path to the externally stored attachment content. Inline binary data in 
+Attachment.data SHALL NOT be populated. Inline content SHALL instead be persisted 
+externally, referenced using this url element, and tagged as 'inline-data-externalized-to-file'.</t>
+  </si>
+  <si>
+    <t>If both data and url are provided, the url SHALL point to the same content as the data contains. Urls may be relative references or may reference transient locations such as a wrapping envelope using cid: though this has ramifications for using signatures. Relative URLs are interpreted relative to the service url, like a resource reference, rather than relative to the resource itself. If a URL is provided, it SHALL resolve to actual data.</t>
+  </si>
+  <si>
+    <t>The data needs to be transmitted by reference.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/logo-small.png</t>
+  </si>
+  <si>
+    <t>Attachment.url</t>
+  </si>
+  <si>
+    <t>RP.1+RP.2 - if they refer to a URL (see v2.6)</t>
+  </si>
+  <si>
+    <t>./reference/literal</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.size</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsignedInt
+</t>
+  </si>
+  <si>
+    <t>Number of bytes of content (if url provided)</t>
+  </si>
+  <si>
+    <t>The number of bytes of data that make up this attachment (before base64 encoding, if that is done).</t>
+  </si>
+  <si>
+    <t>The number of bytes is redundant if the data is provided as a base64binary, but is useful if the data is provided as a url reference.</t>
+  </si>
+  <si>
+    <t>Representing the size allows applications to determine whether they should fetch the content automatically in advance, or refuse to fetch it at all.</t>
+  </si>
+  <si>
+    <t>Attachment.size</t>
+  </si>
+  <si>
+    <t>N/A (needs data type R3 proposal)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.hash</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.hash</t>
+  </si>
+  <si>
+    <t>Hash of the data (sha-1, base64ed)</t>
+  </si>
+  <si>
+    <t>The calculated hash of the data using SHA-1. Represented using base64.</t>
+  </si>
+  <si>
+    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](http://hl7.org/fhir/R4/provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
+  </si>
+  <si>
+    <t>Included so that applications can verify that the contents of a location have not changed due to technical failures (e.g., storage rot, transport glitch, incorrect version).</t>
+  </si>
+  <si>
+    <t>Attachment.hash</t>
+  </si>
+  <si>
+    <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.title</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.title</t>
+  </si>
+  <si>
+    <t>Label to display in place of the data</t>
+  </si>
+  <si>
+    <t>A label or set of text to display in place of the data.</t>
+  </si>
+  <si>
+    <t>Applications need a label to display to a human user in place of the actual data if the data cannot be rendered or perceived by the viewer.</t>
+  </si>
+  <si>
+    <t>Official Corporate Logo</t>
+  </si>
+  <si>
+    <t>Attachment.title</t>
+  </si>
+  <si>
+    <t>./title/data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.creation</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime {http://314e.com/fhir/ig/StructureDefinition/datetime-314e}
+</t>
+  </si>
+  <si>
+    <t>Date attachment was first created</t>
+  </si>
+  <si>
+    <t>The date that the attachment was first created.</t>
+  </si>
+  <si>
+    <t>This is often tracked as an integrity issue for use of the attachment.</t>
+  </si>
+  <si>
+    <t>Attachment.creation</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>Annotation/ notes associated with the diagnostic report</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.extension:tag</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.extension:helperFile</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.contentType</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.language</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.size</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.hash</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.title</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.creation</t>
   </si>
 </sst>
 </file>
@@ -1573,11 +1908,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN43"/>
+  <dimension ref="A1:AN69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.36328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.36328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.06640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.25390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.32421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="54.296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
@@ -1595,7 +1930,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="31.91796875" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
@@ -6498,16 +6833,14 @@
         <v>20</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>384</v>
@@ -6531,14 +6864,2998 @@
         <v>376</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN43" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="D57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="D60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="D61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN43">
+  <autoFilter ref="A1:AN69">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6548,7 +9865,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI42">
+  <conditionalFormatting sqref="A2:AI68">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-lab-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-lab-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$57</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2539" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="486">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1273,19 +1273,28 @@
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.id</t>
+    <t>DiagnosticReport.presentedForm:notes</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>Annotation/ notes associated with the diagnostic report</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.id</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.id</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.extension</t>
+    <t>DiagnosticReport.presentedForm:notes.extension</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.extension</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.extension:tag</t>
+    <t>DiagnosticReport.presentedForm:notes.extension:tag</t>
   </si>
   <si>
     <t>tag</t>
@@ -1304,7 +1313,7 @@
 processing, or application behavior purposes.</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.extension:helperFile</t>
+    <t>DiagnosticReport.presentedForm:notes.extension:helperFile</t>
   </si>
   <si>
     <t>helperFile</t>
@@ -1322,7 +1331,7 @@
 the attachment content.</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.contentType</t>
+    <t>DiagnosticReport.presentedForm:notes.contentType</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.contentType</t>
@@ -1355,7 +1364,7 @@
     <t>./mediaType, ./charset</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.language</t>
+    <t>DiagnosticReport.presentedForm:notes.language</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.language</t>
@@ -1382,7 +1391,7 @@
     <t>./language</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.data</t>
+    <t>DiagnosticReport.presentedForm:notes.data</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.data</t>
@@ -1415,7 +1424,7 @@
     <t>./data</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.url</t>
+    <t>DiagnosticReport.presentedForm:notes.url</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.url</t>
@@ -1451,7 +1460,7 @@
     <t>./reference/literal</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.size</t>
+    <t>DiagnosticReport.presentedForm:notes.size</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.size</t>
@@ -1479,7 +1488,7 @@
     <t>N/A (needs data type R3 proposal)</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.hash</t>
+    <t>DiagnosticReport.presentedForm:notes.hash</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.hash</t>
@@ -1503,7 +1512,7 @@
     <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.title</t>
+    <t>DiagnosticReport.presentedForm:notes.title</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.title</t>
@@ -1518,6 +1527,9 @@
     <t>Applications need a label to display to a human user in place of the actual data if the data cannot be rendered or perceived by the viewer.</t>
   </si>
   <si>
+    <t>Note</t>
+  </si>
+  <si>
     <t>Official Corporate Logo</t>
   </si>
   <si>
@@ -1527,7 +1539,7 @@
     <t>./title/data</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.creation</t>
+    <t>DiagnosticReport.presentedForm:notes.creation</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.creation</t>
@@ -1547,51 +1559,6 @@
   </si>
   <si>
     <t>Attachment.creation</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>Annotation/ notes associated with the diagnostic report</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.extension:tag</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.extension:helperFile</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.contentType</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.language</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.data</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.size</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.hash</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.title</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.creation</t>
   </si>
 </sst>
 </file>
@@ -1908,10 +1875,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN69"/>
+  <dimension ref="A1:AN57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.06640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.46484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.25390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.32421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="54.296875" customWidth="true" bestFit="true" hidden="true"/>
@@ -6993,9 +6960,11 @@
         <v>395</v>
       </c>
       <c r="B45" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C45" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>20</v>
       </c>
@@ -7004,7 +6973,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7016,16 +6985,20 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>103</v>
+        <v>394</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>104</v>
+        <v>397</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -7073,28 +7046,28 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>106</v>
+        <v>384</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>20</v>
+        <v>376</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>107</v>
+        <v>391</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -7102,21 +7075,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7128,17 +7101,15 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7175,31 +7146,31 @@
         <v>20</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7216,16 +7187,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7244,15 +7213,17 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>401</v>
+        <v>110</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>402</v>
+        <v>111</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7289,16 +7260,16 @@
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>117</v>
@@ -7322,7 +7293,7 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
@@ -7330,13 +7301,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>20</v>
@@ -7346,7 +7317,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7358,13 +7329,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7444,12 +7415,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7467,21 +7440,19 @@
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>165</v>
+        <v>409</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>412</v>
-      </c>
       <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>413</v>
-      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7493,7 +7464,7 @@
         <v>20</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>414</v>
+        <v>20</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>20</v>
@@ -7505,13 +7476,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>415</v>
+        <v>20</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>416</v>
+        <v>20</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7529,28 +7500,28 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>417</v>
+        <v>117</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>418</v>
+        <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>419</v>
+        <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>20</v>
@@ -7558,10 +7529,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7587,14 +7558,14 @@
         <v>165</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7607,7 +7578,7 @@
         <v>20</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>20</v>
@@ -7619,13 +7590,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>169</v>
+        <v>229</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>170</v>
+        <v>418</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7643,7 +7614,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7661,10 +7632,10 @@
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>20</v>
+        <v>421</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>20</v>
@@ -7672,10 +7643,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7686,7 +7657,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7695,22 +7666,20 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>431</v>
+        <v>165</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7723,7 +7692,7 @@
         <v>20</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>20</v>
+        <v>428</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>20</v>
@@ -7735,13 +7704,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>20</v>
+        <v>429</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7759,7 +7728,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7777,10 +7746,10 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>437</v>
+        <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>20</v>
@@ -7788,10 +7757,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7799,10 +7768,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -7811,22 +7780,22 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7839,7 +7808,7 @@
         <v>20</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>446</v>
+        <v>20</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>20</v>
@@ -7875,7 +7844,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7893,10 +7862,10 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>20</v>
@@ -7904,10 +7873,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7915,7 +7884,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>89</v>
@@ -7930,19 +7899,19 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7955,7 +7924,7 @@
         <v>20</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>20</v>
+        <v>449</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>20</v>
@@ -7991,7 +7960,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8009,10 +7978,10 @@
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>20</v>
+        <v>451</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>20</v>
@@ -8020,10 +7989,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8046,19 +8015,19 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8107,7 +8076,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8128,7 +8097,7 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>20</v>
@@ -8136,10 +8105,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8147,7 +8116,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>89</v>
@@ -8162,17 +8131,19 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>103</v>
+        <v>434</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8182,10 +8153,10 @@
         <v>20</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>386</v>
+        <v>20</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>472</v>
+        <v>20</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>20</v>
@@ -8221,7 +8192,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8242,7 +8213,7 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>20</v>
@@ -8250,10 +8221,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8261,7 +8232,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>89</v>
@@ -8276,17 +8247,17 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>477</v>
+        <v>103</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8296,10 +8267,10 @@
         <v>20</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>20</v>
+        <v>475</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>20</v>
+        <v>476</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>20</v>
@@ -8335,7 +8306,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8356,7 +8327,7 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>20</v>
@@ -8364,14 +8335,12 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>20</v>
       </c>
@@ -8380,7 +8349,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8389,22 +8358,20 @@
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>394</v>
+        <v>481</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8453,13 +8420,13 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>384</v>
+        <v>485</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
@@ -8471,1391 +8438,17 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>376</v>
+        <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>391</v>
+        <v>461</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="D60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="D61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="P62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AN69" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN69">
+  <autoFilter ref="A1:AN57">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9865,7 +8458,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI56">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-lab-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-lab-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2140" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -811,6 +811,22 @@
     &lt;code value="LAB"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:subCategory</t>
+  </si>
+  <si>
+    <t>subCategory</t>
+  </si>
+  <si>
+    <t>Optional detailed subcategory</t>
+  </si>
+  <si>
+    <t>More granular operational sub-classification of the
+diagnostic report.</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/ValueSet/procedure-category-subcategory-314e</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -1875,7 +1891,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN57"/>
+  <dimension ref="A1:AN58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.46484375" customWidth="true" bestFit="true"/>
@@ -1903,7 +1919,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="85.89453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.94921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="57.36328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
@@ -4664,15 +4680,17 @@
         <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="D25" t="s" s="2">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>89</v>
@@ -4696,7 +4714,7 @@
         <v>254</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4722,13 +4740,11 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4746,13 +4762,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -4761,28 +4777,28 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>258</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>261</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4801,18 +4817,18 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -4836,13 +4852,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>20</v>
+        <v>262</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4860,10 +4876,10 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>89</v>
@@ -4875,32 +4891,32 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>89</v>
@@ -4915,19 +4931,17 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4976,7 +4990,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4991,28 +5005,28 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5031,19 +5045,19 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5092,7 +5106,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5101,34 +5115,34 @@
         <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5147,19 +5161,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5208,7 +5222,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5217,41 +5231,41 @@
         <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>20</v>
+        <v>296</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>90</v>
@@ -5263,19 +5277,19 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5324,43 +5338,43 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>20</v>
+        <v>307</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>313</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5370,7 +5384,7 @@
         <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
@@ -5379,19 +5393,19 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5440,7 +5454,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5455,28 +5469,28 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>20</v>
+        <v>323</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5492,22 +5506,22 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="N32" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="O32" t="s" s="2">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5556,7 +5570,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5571,28 +5585,28 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>20</v>
+        <v>321</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5602,7 +5616,7 @@
         <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
@@ -5611,19 +5625,19 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5672,7 +5686,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5690,25 +5704,25 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>339</v>
+        <v>275</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>20</v>
+        <v>337</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5718,7 +5732,7 @@
         <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>20</v>
@@ -5727,18 +5741,20 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5786,7 +5802,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5804,10 +5820,10 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>20</v>
+        <v>343</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -5815,14 +5831,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>347</v>
+        <v>20</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5838,21 +5854,21 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>351</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5900,7 +5916,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5918,10 +5934,10 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -5929,21 +5945,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>20</v>
+        <v>352</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5952,19 +5968,21 @@
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>103</v>
+        <v>353</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>104</v>
+        <v>354</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>105</v>
+        <v>355</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -6012,28 +6030,28 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>106</v>
+        <v>351</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>20</v>
+        <v>357</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>107</v>
+        <v>344</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
@@ -6041,21 +6059,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6067,17 +6085,15 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6126,19 +6142,19 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -6155,14 +6171,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>356</v>
+        <v>109</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6175,26 +6191,24 @@
         <v>20</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>357</v>
+        <v>111</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>358</v>
+        <v>112</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O38" t="s" s="2">
-        <v>202</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6242,7 +6256,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>359</v>
+        <v>117</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6263,7 +6277,7 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6278,38 +6292,38 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>20</v>
+        <v>361</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>363</v>
+        <v>113</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>364</v>
+        <v>202</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6358,19 +6372,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6379,7 +6393,7 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>365</v>
+        <v>188</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -6387,10 +6401,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6398,7 +6412,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>89</v>
@@ -6410,19 +6424,23 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6470,10 +6488,10 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>89</v>
@@ -6506,11 +6524,11 @@
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>372</v>
+        <v>20</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>89</v>
@@ -6522,10 +6540,10 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>103</v>
+        <v>372</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>373</v>
@@ -6534,9 +6552,7 @@
         <v>374</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>375</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6587,7 +6603,7 @@
         <v>371</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>89</v>
@@ -6602,10 +6618,10 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>376</v>
+        <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6613,21 +6629,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>20</v>
+        <v>377</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6639,16 +6655,18 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>238</v>
+        <v>103</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6672,13 +6690,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>382</v>
+        <v>20</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6696,13 +6714,13 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
@@ -6714,10 +6732,10 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -6725,10 +6743,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6751,20 +6769,16 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>389</v>
-      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
@@ -6788,29 +6802,31 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>20</v>
+        <v>386</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>20</v>
+        <v>387</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6828,10 +6844,10 @@
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -6839,14 +6855,12 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>20</v>
       </c>
@@ -6867,19 +6881,19 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6916,19 +6930,17 @@
         <v>20</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6946,10 +6958,10 @@
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -6957,13 +6969,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>20</v>
@@ -6985,19 +6997,19 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O45" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7046,7 +7058,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7064,10 +7076,10 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -7075,12 +7087,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="D46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7089,7 +7103,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7101,16 +7115,20 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>103</v>
+        <v>399</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>104</v>
+        <v>402</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7158,28 +7176,28 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>106</v>
+        <v>389</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>20</v>
+        <v>381</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>107</v>
+        <v>396</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7187,21 +7205,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7213,17 +7231,15 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7260,31 +7276,31 @@
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7301,16 +7317,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7329,15 +7343,17 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>404</v>
+        <v>110</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>405</v>
+        <v>111</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7374,16 +7390,16 @@
         <v>20</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>117</v>
@@ -7407,7 +7423,7 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
@@ -7418,7 +7434,7 @@
         <v>407</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>408</v>
@@ -7431,7 +7447,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7532,9 +7548,11 @@
         <v>412</v>
       </c>
       <c r="B50" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C50" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>20</v>
       </c>
@@ -7552,21 +7570,19 @@
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>165</v>
+        <v>414</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>416</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>20</v>
       </c>
@@ -7578,7 +7594,7 @@
         <v>20</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>417</v>
+        <v>20</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>20</v>
@@ -7590,13 +7606,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>418</v>
+        <v>20</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>419</v>
+        <v>20</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7614,28 +7630,28 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>420</v>
+        <v>117</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>421</v>
+        <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>422</v>
+        <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>20</v>
@@ -7643,10 +7659,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7672,14 +7688,14 @@
         <v>165</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7692,7 +7708,7 @@
         <v>20</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>20</v>
@@ -7704,13 +7720,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>169</v>
+        <v>229</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>170</v>
+        <v>423</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7728,7 +7744,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7746,10 +7762,10 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>20</v>
+        <v>426</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>20</v>
@@ -7757,10 +7773,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7771,7 +7787,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -7780,22 +7796,20 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>434</v>
+        <v>165</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7808,7 +7822,7 @@
         <v>20</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>20</v>
+        <v>433</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>20</v>
@@ -7820,13 +7834,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>20</v>
+        <v>434</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7844,7 +7858,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7862,10 +7876,10 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>440</v>
+        <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>20</v>
@@ -7873,10 +7887,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7884,10 +7898,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -7896,22 +7910,22 @@
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7924,7 +7938,7 @@
         <v>20</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>449</v>
+        <v>20</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>20</v>
@@ -7960,7 +7974,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7978,10 +7992,10 @@
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>20</v>
@@ -7989,10 +8003,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8000,7 +8014,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>89</v>
@@ -8015,19 +8029,19 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8040,7 +8054,7 @@
         <v>20</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>20</v>
+        <v>454</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>20</v>
@@ -8076,7 +8090,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8094,10 +8108,10 @@
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>20</v>
@@ -8105,10 +8119,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8131,19 +8145,19 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8192,7 +8206,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8213,7 +8227,7 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>20</v>
@@ -8221,10 +8235,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8232,7 +8246,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>89</v>
@@ -8247,17 +8261,19 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>103</v>
+        <v>439</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="O56" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8267,10 +8283,10 @@
         <v>20</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>475</v>
+        <v>20</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>476</v>
+        <v>20</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>20</v>
@@ -8306,7 +8322,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8327,7 +8343,7 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>20</v>
@@ -8335,10 +8351,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8346,7 +8362,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>89</v>
@@ -8361,17 +8377,17 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>481</v>
+        <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8381,10 +8397,10 @@
         <v>20</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>20</v>
+        <v>480</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>20</v>
+        <v>481</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>20</v>
@@ -8420,7 +8436,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8441,14 +8457,128 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN57">
+  <autoFilter ref="A1:AN58">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8458,7 +8588,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI56">
+  <conditionalFormatting sqref="A2:AI57">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-lab-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-lab-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -701,7 +701,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-careplan|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-immunizationrecommendation|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-medicationrequest|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-nutritionorder|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-servicerequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -870,7 +870,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -902,7 +902,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1012,7 +1012,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-practitioner|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-practitionerrole|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1047,7 +1047,7 @@
 Reported by</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/careteam-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1066,7 +1066,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/specimen-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1092,7 +1092,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-observation-lab) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1117,7 +1117,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/imagingstudy-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1200,7 +1200,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/media-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-lab-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-lab-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-lab-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-lab-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
